--- a/sample_data/SAP_billing_documents_sample.xlsx
+++ b/sample_data/SAP_billing_documents_sample.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46291</v>
+        <v>46310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46291</v>
+        <v>46310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46291</v>
+        <v>46310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46291</v>
+        <v>46310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46291</v>
+        <v>46310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46291</v>
+        <v>46310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/sample_data/SAP_billing_documents_sample.xlsx
+++ b/sample_data/SAP_billing_documents_sample.xlsx
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46310</v>
+        <v>46316</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46310</v>
+        <v>46316</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46310</v>
+        <v>46316</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46310</v>
+        <v>46316</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46310</v>
+        <v>46316</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46310</v>
+        <v>46316</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
